--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/95.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/95.xlsx
@@ -426,13 +426,13 @@
         <v>-1.282240254684058</v>
       </c>
       <c r="E2">
-        <v>-8.446815203572866</v>
+        <v>-1.376454393709045</v>
       </c>
       <c r="F2">
-        <v>-3.813955260971144</v>
+        <v>-3.609894406598111</v>
       </c>
       <c r="G2">
-        <v>-6.228580707892559</v>
+        <v>-3.229888558420718</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-1.119197247791928</v>
       </c>
       <c r="E3">
-        <v>-8.442970529140354</v>
+        <v>-3.17924895311063</v>
       </c>
       <c r="F3">
-        <v>-3.925419550324443</v>
+        <v>-3.945712894958225</v>
       </c>
       <c r="G3">
-        <v>-5.013875338623175</v>
+        <v>-2.614491248125597</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-0.945956489969114</v>
       </c>
       <c r="E4">
-        <v>-9.248862292019378</v>
+        <v>-3.274591444868122</v>
       </c>
       <c r="F4">
-        <v>-4.191379330504266</v>
+        <v>-3.825011480696309</v>
       </c>
       <c r="G4">
-        <v>-5.490421747910184</v>
+        <v>-2.501998910701162</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-0.7703772841320004</v>
       </c>
       <c r="E5">
-        <v>-11.02047377940415</v>
+        <v>-4.349927411203533</v>
       </c>
       <c r="F5">
-        <v>-3.740536229693621</v>
+        <v>-3.631084044761722</v>
       </c>
       <c r="G5">
-        <v>-4.749889126776151</v>
+        <v>-2.1432483327925</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-0.5815781348940998</v>
       </c>
       <c r="E6">
-        <v>-10.1949691955979</v>
+        <v>-6.917626515240717</v>
       </c>
       <c r="F6">
-        <v>-3.698948044236072</v>
+        <v>-3.777054806646037</v>
       </c>
       <c r="G6">
-        <v>-3.995743542384635</v>
+        <v>-2.139636527609155</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-0.3779437568465314</v>
       </c>
       <c r="E7">
-        <v>-12.424916594247</v>
+        <v>-7.751078570930424</v>
       </c>
       <c r="F7">
-        <v>-3.659466397083842</v>
+        <v>-3.29607984155856</v>
       </c>
       <c r="G7">
-        <v>-4.908202725009639</v>
+        <v>-3.093464287292891</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-0.1534000770355031</v>
       </c>
       <c r="E8">
-        <v>-14.31612960864835</v>
+        <v>-8.63736433286762</v>
       </c>
       <c r="F8">
-        <v>-3.886000030727423</v>
+        <v>-3.451894093290341</v>
       </c>
       <c r="G8">
-        <v>-4.804420432899026</v>
+        <v>-2.364406016997973</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>0.09576886855061907</v>
       </c>
       <c r="E9">
-        <v>-13.68510939804952</v>
+        <v>-9.417258126468608</v>
       </c>
       <c r="F9">
-        <v>-3.997316870683023</v>
+        <v>-3.191742825338948</v>
       </c>
       <c r="G9">
-        <v>-5.070412835342848</v>
+        <v>-2.742685503042795</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>0.3740596174932397</v>
       </c>
       <c r="E10">
-        <v>-14.85223753252041</v>
+        <v>-10.20518996143321</v>
       </c>
       <c r="F10">
-        <v>-3.777516207289397</v>
+        <v>-3.086168228219554</v>
       </c>
       <c r="G10">
-        <v>-3.30223722063595</v>
+        <v>-2.600778968501936</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>0.6854414346386069</v>
       </c>
       <c r="E11">
-        <v>-16.33630450584013</v>
+        <v>-11.10444527292838</v>
       </c>
       <c r="F11">
-        <v>-3.360041402198321</v>
+        <v>-3.005802507902155</v>
       </c>
       <c r="G11">
-        <v>-4.571430858936199</v>
+        <v>-2.146774063791824</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>1.028102153510437</v>
       </c>
       <c r="E12">
-        <v>-16.75249390951508</v>
+        <v>-11.89397565921769</v>
       </c>
       <c r="F12">
-        <v>-3.704831109530754</v>
+        <v>-2.945840305083109</v>
       </c>
       <c r="G12">
-        <v>-2.923487637124552</v>
+        <v>-1.892143453638781</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>1.393880940763033</v>
       </c>
       <c r="E13">
-        <v>-17.13077545727181</v>
+        <v>-12.9227317419102</v>
       </c>
       <c r="F13">
-        <v>-3.055439939412707</v>
+        <v>-2.697292807710132</v>
       </c>
       <c r="G13">
-        <v>-2.672498627064706</v>
+        <v>-2.343585996101496</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>1.770259777510202</v>
       </c>
       <c r="E14">
-        <v>-18.30926100455394</v>
+        <v>-13.51963895780925</v>
       </c>
       <c r="F14">
-        <v>-3.286509712954017</v>
+        <v>-2.338668536383545</v>
       </c>
       <c r="G14">
-        <v>-2.445573972529824</v>
+        <v>-1.120491704435599</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>2.137204662321617</v>
       </c>
       <c r="E15">
-        <v>-18.57383256997807</v>
+        <v>-14.99763324748468</v>
       </c>
       <c r="F15">
-        <v>-3.300446994506119</v>
+        <v>-2.189477910404548</v>
       </c>
       <c r="G15">
-        <v>-2.134975279489862</v>
+        <v>-1.208307235410307</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>2.472364682789741</v>
       </c>
       <c r="E16">
-        <v>-19.29234289840509</v>
+        <v>-16.64840693444877</v>
       </c>
       <c r="F16">
-        <v>-2.876317085700953</v>
+        <v>-2.217834583337181</v>
       </c>
       <c r="G16">
-        <v>-2.452440043978272</v>
+        <v>-0.9004331213491648</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>2.757088490332729</v>
       </c>
       <c r="E17">
-        <v>-19.72043313177219</v>
+        <v>-17.17921654373186</v>
       </c>
       <c r="F17">
-        <v>-3.021456166712857</v>
+        <v>-1.710717171384754</v>
       </c>
       <c r="G17">
-        <v>-1.335895660493818</v>
+        <v>-0.9846732631414594</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>2.975954043689222</v>
       </c>
       <c r="E18">
-        <v>-22.04800537307865</v>
+        <v>-17.68293682150107</v>
       </c>
       <c r="F18">
-        <v>-2.498038141008142</v>
+        <v>-1.379509375988622</v>
       </c>
       <c r="G18">
-        <v>-1.323063985983603</v>
+        <v>0.05956218467423328</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>3.122110075939326</v>
       </c>
       <c r="E19">
-        <v>-22.949140001287</v>
+        <v>-18.73088910551209</v>
       </c>
       <c r="F19">
-        <v>-1.78430270451024</v>
+        <v>-1.245377641025118</v>
       </c>
       <c r="G19">
-        <v>-0.9766253269354912</v>
+        <v>-0.5254112121149854</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>3.196611521713181</v>
       </c>
       <c r="E20">
-        <v>-23.12347266516028</v>
+        <v>-19.74042634451606</v>
       </c>
       <c r="F20">
-        <v>-1.735502752443918</v>
+        <v>-0.8079714878552839</v>
       </c>
       <c r="G20">
-        <v>-0.4119753692118582</v>
+        <v>-0.411313260104004</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>3.203583163060067</v>
       </c>
       <c r="E21">
-        <v>-23.88739453093622</v>
+        <v>-20.87427925197858</v>
       </c>
       <c r="F21">
-        <v>-1.87363715869775</v>
+        <v>-0.1995828474410066</v>
       </c>
       <c r="G21">
-        <v>-0.2589089856581157</v>
+        <v>-0.01427622303367127</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.153348757874862</v>
       </c>
       <c r="E22">
-        <v>-24.5594246021485</v>
+        <v>-22.22697519433579</v>
       </c>
       <c r="F22">
-        <v>-1.593264614076618</v>
+        <v>-0.3572750080749345</v>
       </c>
       <c r="G22">
-        <v>-0.8230921564607113</v>
+        <v>0.4038920262138295</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>3.058644007829275</v>
       </c>
       <c r="E23">
-        <v>-24.46555386444351</v>
+        <v>-21.65942607542847</v>
       </c>
       <c r="F23">
-        <v>-1.411630150399576</v>
+        <v>0.04275106604357194</v>
       </c>
       <c r="G23">
-        <v>-0.206933420691558</v>
+        <v>-0.1337968486379789</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>2.930919141945242</v>
       </c>
       <c r="E24">
-        <v>-24.94694423688089</v>
+        <v>-22.79371824486974</v>
       </c>
       <c r="F24">
-        <v>-0.7838312050029007</v>
+        <v>0.5753921344110569</v>
       </c>
       <c r="G24">
-        <v>-0.6804374386279766</v>
+        <v>0.3409287606024308</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>2.780893295736493</v>
       </c>
       <c r="E25">
-        <v>-24.73374368059977</v>
+        <v>-22.8252183100671</v>
       </c>
       <c r="F25">
-        <v>-0.3476270129345287</v>
+        <v>0.7802299974079158</v>
       </c>
       <c r="G25">
-        <v>-0.7634030203876518</v>
+        <v>-0.2255055811668694</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>2.612412787365769</v>
       </c>
       <c r="E26">
-        <v>-25.80134954180409</v>
+        <v>-22.47946479110746</v>
       </c>
       <c r="F26">
-        <v>-0.5275227334330945</v>
+        <v>1.025758095597689</v>
       </c>
       <c r="G26">
-        <v>-0.9539911270834941</v>
+        <v>-0.2776201890460764</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.424454620782246</v>
       </c>
       <c r="E27">
-        <v>-25.07096555452896</v>
+        <v>-23.24351798262961</v>
       </c>
       <c r="F27">
-        <v>-0.4204752990715228</v>
+        <v>1.194117143277466</v>
       </c>
       <c r="G27">
-        <v>-0.2783749934290302</v>
+        <v>-0.3182107879030804</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.219627072923989</v>
       </c>
       <c r="E28">
-        <v>-26.11571620741656</v>
+        <v>-23.98406839405196</v>
       </c>
       <c r="F28">
-        <v>-0.7233620413333425</v>
+        <v>0.8216450540782799</v>
       </c>
       <c r="G28">
-        <v>-1.232159716020756</v>
+        <v>-0.4388702411728974</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.99802839652394</v>
       </c>
       <c r="E29">
-        <v>-25.7423163546401</v>
+        <v>-24.13579038720495</v>
       </c>
       <c r="F29">
-        <v>-0.820353923792331</v>
+        <v>1.151689821640881</v>
       </c>
       <c r="G29">
-        <v>-1.013680263156554</v>
+        <v>-1.096841167103046</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.761089167114062</v>
       </c>
       <c r="E30">
-        <v>-25.98030124916519</v>
+        <v>-22.26563477693927</v>
       </c>
       <c r="F30">
-        <v>-0.2292185196435617</v>
+        <v>0.9137114639602225</v>
       </c>
       <c r="G30">
-        <v>-2.27497825034564</v>
+        <v>-0.9401662889114976</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.514997657104022</v>
       </c>
       <c r="E31">
-        <v>-25.60629910934571</v>
+        <v>-22.93152876587116</v>
       </c>
       <c r="F31">
-        <v>-0.740389961665289</v>
+        <v>0.8678861792373539</v>
       </c>
       <c r="G31">
-        <v>-1.494076836905735</v>
+        <v>-1.991880259100404</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.263885598353492</v>
       </c>
       <c r="E32">
-        <v>-24.98606119535915</v>
+        <v>-22.46261433932492</v>
       </c>
       <c r="F32">
-        <v>-0.4182337368795473</v>
+        <v>1.309331451863238</v>
       </c>
       <c r="G32">
-        <v>-1.781031613704222</v>
+        <v>-1.729175228377078</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.015222124387766</v>
       </c>
       <c r="E33">
-        <v>-24.82425429059107</v>
+        <v>-21.43948714982394</v>
       </c>
       <c r="F33">
-        <v>-0.2372197203872022</v>
+        <v>1.187853028977496</v>
       </c>
       <c r="G33">
-        <v>-1.723567164233553</v>
+        <v>-1.35592115046087</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.7789826477212904</v>
       </c>
       <c r="E34">
-        <v>-25.16827340400578</v>
+        <v>-21.5480392002618</v>
       </c>
       <c r="F34">
-        <v>-0.3897544655713003</v>
+        <v>0.9140577215345927</v>
       </c>
       <c r="G34">
-        <v>-2.640154597146027</v>
+        <v>-2.25190374793692</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.5621467823786941</v>
       </c>
       <c r="E35">
-        <v>-24.04095961301033</v>
+        <v>-21.48709952554058</v>
       </c>
       <c r="F35">
-        <v>-0.2542285882688844</v>
+        <v>1.153780620965547</v>
       </c>
       <c r="G35">
-        <v>-3.1760955039531</v>
+        <v>-2.275663533272269</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.3745307980535971</v>
       </c>
       <c r="E36">
-        <v>-22.30836092920164</v>
+        <v>-21.21880555448214</v>
       </c>
       <c r="F36">
-        <v>-0.7267542058478064</v>
+        <v>0.9305588001983589</v>
       </c>
       <c r="G36">
-        <v>-2.343016582268742</v>
+        <v>-2.386100021916817</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.2243744380509199</v>
       </c>
       <c r="E37">
-        <v>-22.27747220799532</v>
+        <v>-19.79866252025469</v>
       </c>
       <c r="F37">
-        <v>-0.3607566362689009</v>
+        <v>0.7592921829347555</v>
       </c>
       <c r="G37">
-        <v>-3.150902252399247</v>
+        <v>-2.384464612420417</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.1156394204796079</v>
       </c>
       <c r="E38">
-        <v>-21.82395459307515</v>
+        <v>-20.05583003067629</v>
       </c>
       <c r="F38">
-        <v>-0.412694444057027</v>
+        <v>1.039885073285032</v>
       </c>
       <c r="G38">
-        <v>-2.043329447326217</v>
+        <v>-2.275855544913547</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.05588786186504437</v>
       </c>
       <c r="E39">
-        <v>-21.51567872500299</v>
+        <v>-19.65651372115392</v>
       </c>
       <c r="F39">
-        <v>-0.6049957947799183</v>
+        <v>0.6232576880470206</v>
       </c>
       <c r="G39">
-        <v>-3.487180847187335</v>
+        <v>-1.803894241198429</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.04852435719167814</v>
       </c>
       <c r="E40">
-        <v>-21.43926072612355</v>
+        <v>-18.03356750696697</v>
       </c>
       <c r="F40">
-        <v>-0.456237576585183</v>
+        <v>0.6597423019359221</v>
       </c>
       <c r="G40">
-        <v>-2.875689980628554</v>
+        <v>-2.156023728028548</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.09251141496880774</v>
       </c>
       <c r="E41">
-        <v>-19.53607895491993</v>
+        <v>-17.98028548179272</v>
       </c>
       <c r="F41">
-        <v>-0.6655403398831313</v>
+        <v>0.6855343493894875</v>
       </c>
       <c r="G41">
-        <v>-3.051592507312189</v>
+        <v>-1.88760469570444</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.1895175405635139</v>
       </c>
       <c r="E42">
-        <v>-20.57795855528667</v>
+        <v>-16.93630014101241</v>
       </c>
       <c r="F42">
-        <v>-0.8434015900404216</v>
+        <v>0.03319336295007123</v>
       </c>
       <c r="G42">
-        <v>-2.664887682869922</v>
+        <v>-1.651185396562928</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.3352020318342918</v>
       </c>
       <c r="E43">
-        <v>-20.28382058306646</v>
+        <v>-15.70218229054605</v>
       </c>
       <c r="F43">
-        <v>-1.367194037811202</v>
+        <v>0.4589609541105723</v>
       </c>
       <c r="G43">
-        <v>-2.255710875307082</v>
+        <v>-1.2235986452562</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.5233693185653812</v>
       </c>
       <c r="E44">
-        <v>-17.93277273250424</v>
+        <v>-15.27811787057177</v>
       </c>
       <c r="F44">
-        <v>-0.9007395249273977</v>
+        <v>0.6620667008681775</v>
       </c>
       <c r="G44">
-        <v>-1.942973569848751</v>
+        <v>-1.06384495971313</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.7494812498432668</v>
       </c>
       <c r="E45">
-        <v>-17.51560064996963</v>
+        <v>-14.53901204235787</v>
       </c>
       <c r="F45">
-        <v>-0.8168217651867938</v>
+        <v>0.5561541298484411</v>
       </c>
       <c r="G45">
-        <v>-1.932717499768088</v>
+        <v>-0.8860653537087279</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>1.003662820599523</v>
       </c>
       <c r="E46">
-        <v>-16.98650733233545</v>
+        <v>-13.45090125084682</v>
       </c>
       <c r="F46">
-        <v>-0.8233807782821604</v>
+        <v>-0.0761511342194635</v>
       </c>
       <c r="G46">
-        <v>-1.499893465418234</v>
+        <v>-0.5942043484210408</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>1.276353558982702</v>
       </c>
       <c r="E47">
-        <v>-16.82177503335842</v>
+        <v>-12.61741749583906</v>
       </c>
       <c r="F47">
-        <v>-1.059781924427889</v>
+        <v>0.1294745061774578</v>
       </c>
       <c r="G47">
-        <v>-1.98576568148937</v>
+        <v>-0.5128874183399226</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>1.557869062926766</v>
       </c>
       <c r="E48">
-        <v>-15.62547446933012</v>
+        <v>-11.58318648807127</v>
       </c>
       <c r="F48">
-        <v>-0.6564705451898796</v>
+        <v>-0.22413151542297</v>
       </c>
       <c r="G48">
-        <v>-1.896321362109341</v>
+        <v>-0.2649176258118928</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>1.8343407807642</v>
       </c>
       <c r="E49">
-        <v>-15.34499437471704</v>
+        <v>-11.19187652059447</v>
       </c>
       <c r="F49">
-        <v>-1.031100531473359</v>
+        <v>0.0436423893689842</v>
       </c>
       <c r="G49">
-        <v>-2.658594335799767</v>
+        <v>0.01581332537276455</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>2.094878127133623</v>
       </c>
       <c r="E50">
-        <v>-14.58585457749321</v>
+        <v>-10.69532934565341</v>
       </c>
       <c r="F50">
-        <v>-1.078968570211531</v>
+        <v>-0.1444723925001583</v>
       </c>
       <c r="G50">
-        <v>-2.570851636826924</v>
+        <v>-0.6859826024062559</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>2.328424600599368</v>
       </c>
       <c r="E51">
-        <v>-13.10206384108796</v>
+        <v>-10.01025726929903</v>
       </c>
       <c r="F51">
-        <v>-0.7969898211963709</v>
+        <v>-0.05801154483295993</v>
       </c>
       <c r="G51">
-        <v>-1.071376450814972</v>
+        <v>-0.1520313334682846</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>2.522918662348705</v>
       </c>
       <c r="E52">
-        <v>-12.41123607426983</v>
+        <v>-8.513343015219553</v>
       </c>
       <c r="F52">
-        <v>-0.9921250168042393</v>
+        <v>-0.08470237091856279</v>
       </c>
       <c r="G52">
-        <v>-1.002808431605587</v>
+        <v>-0.587176060241168</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>2.670972319924378</v>
       </c>
       <c r="E53">
-        <v>-11.41979461740052</v>
+        <v>-7.710815908528226</v>
       </c>
       <c r="F53">
-        <v>-0.9100130980017382</v>
+        <v>0.1963436364010451</v>
       </c>
       <c r="G53">
-        <v>-2.327420602233235</v>
+        <v>-0.4096381240611328</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>2.76589422900405</v>
       </c>
       <c r="E54">
-        <v>-12.50013907598841</v>
+        <v>-7.232119978125408</v>
       </c>
       <c r="F54">
-        <v>-1.173732972724392</v>
+        <v>-0.1368961442341541</v>
       </c>
       <c r="G54">
-        <v>-2.809796882214901</v>
+        <v>-0.3951975244188319</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>2.802488828663925</v>
       </c>
       <c r="E55">
-        <v>-10.78478934967494</v>
+        <v>-6.364011510855001</v>
       </c>
       <c r="F55">
-        <v>-1.18951254338032</v>
+        <v>-0.1094862952429212</v>
       </c>
       <c r="G55">
-        <v>-1.98931127576193</v>
+        <v>-0.3860537976393649</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>2.779800655160359</v>
       </c>
       <c r="E56">
-        <v>-10.75380100204045</v>
+        <v>-5.518808065115389</v>
       </c>
       <c r="F56">
-        <v>-0.8275135032547271</v>
+        <v>-0.230118126643002</v>
       </c>
       <c r="G56">
-        <v>-3.313635428927661</v>
+        <v>-1.500919734535408</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>2.697925257805563</v>
       </c>
       <c r="E57">
-        <v>-11.16655329394358</v>
+        <v>-4.45839794910926</v>
       </c>
       <c r="F57">
-        <v>-0.9615077292293667</v>
+        <v>-0.2690977831491356</v>
       </c>
       <c r="G57">
-        <v>-3.405311056001159</v>
+        <v>-1.465460481264275</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>2.559300364411636</v>
       </c>
       <c r="E58">
-        <v>-9.47174019725489</v>
+        <v>-4.628677628745681</v>
       </c>
       <c r="F58">
-        <v>-1.155886625398479</v>
+        <v>-0.1829981036695577</v>
       </c>
       <c r="G58">
-        <v>-3.478358243325177</v>
+        <v>-1.174764788006411</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>2.370645932206181</v>
       </c>
       <c r="E59">
-        <v>-8.358636757695509</v>
+        <v>-3.332071365447482</v>
       </c>
       <c r="F59">
-        <v>-0.9734453318711104</v>
+        <v>-0.3227726773809323</v>
       </c>
       <c r="G59">
-        <v>-3.239922821950249</v>
+        <v>-1.637747892219026</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>2.139246585022453</v>
       </c>
       <c r="E60">
-        <v>-10.512655232658</v>
+        <v>-3.707078826496672</v>
       </c>
       <c r="F60">
-        <v>-0.7514569501666905</v>
+        <v>-0.4994634443980668</v>
       </c>
       <c r="G60">
-        <v>-3.000451199821528</v>
+        <v>-1.723063961311583</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>1.874212761346262</v>
       </c>
       <c r="E61">
-        <v>-8.027623421630837</v>
+        <v>-2.925695164947159</v>
       </c>
       <c r="F61">
-        <v>-1.225880357465426</v>
+        <v>-0.5274771732259406</v>
       </c>
       <c r="G61">
-        <v>-3.976502651710391</v>
+        <v>-2.471657760833741</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>1.5864099753601</v>
       </c>
       <c r="E62">
-        <v>-6.894762249975989</v>
+        <v>-3.026014449639081</v>
       </c>
       <c r="F62">
-        <v>-1.129376383406687</v>
+        <v>-0.3341428483517583</v>
       </c>
       <c r="G62">
-        <v>-3.673501660683057</v>
+        <v>-2.705349170450895</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>1.285366237719103</v>
       </c>
       <c r="E63">
-        <v>-8.497022394895907</v>
+        <v>-1.583152061315151</v>
       </c>
       <c r="F63">
-        <v>-1.104316612737196</v>
+        <v>-0.5010505963418307</v>
       </c>
       <c r="G63">
-        <v>-3.172894206416625</v>
+        <v>-2.935845903622651</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.9816481612849924</v>
       </c>
       <c r="E64">
-        <v>-7.085401948750897</v>
+        <v>-1.631565976931155</v>
       </c>
       <c r="F64">
-        <v>-1.72867700504485</v>
+        <v>-0.2446750270123977</v>
       </c>
       <c r="G64">
-        <v>-4.110636025325042</v>
+        <v>-3.139696055748813</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>0.685284565855064</v>
       </c>
       <c r="E65">
-        <v>-6.372556741307474</v>
+        <v>-1.968855777970459</v>
       </c>
       <c r="F65">
-        <v>-1.58414263223699</v>
+        <v>-0.819337516989096</v>
       </c>
       <c r="G65">
-        <v>-4.825535092348498</v>
+        <v>-3.189804473031222</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>0.4038026339428398</v>
       </c>
       <c r="E66">
-        <v>-5.781015767107519</v>
+        <v>-0.9813359795917914</v>
       </c>
       <c r="F66">
-        <v>-1.113379780491225</v>
+        <v>-0.6206295727729534</v>
       </c>
       <c r="G66">
-        <v>-3.714367034819821</v>
+        <v>-3.993571824510874</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>0.1457214237760342</v>
       </c>
       <c r="E67">
-        <v>-7.236775249405293</v>
+        <v>-0.5481874407581218</v>
       </c>
       <c r="F67">
-        <v>-1.540288861932784</v>
+        <v>-0.9534932746072815</v>
       </c>
       <c r="G67">
-        <v>-5.33413420354673</v>
+        <v>-3.85354567983632</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.08296596195996284</v>
       </c>
       <c r="E68">
-        <v>-7.726905576677479</v>
+        <v>-0.9017525773809926</v>
       </c>
       <c r="F68">
-        <v>-1.883734128970473</v>
+        <v>-0.5643527765289633</v>
       </c>
       <c r="G68">
-        <v>-5.576982582125508</v>
+        <v>-3.638780659067181</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.2793443267989147</v>
       </c>
       <c r="E69">
-        <v>-6.326719527401836</v>
+        <v>-0.2240483282370929</v>
       </c>
       <c r="F69">
-        <v>-1.016532033960324</v>
+        <v>-1.072123770362199</v>
       </c>
       <c r="G69">
-        <v>-4.247437698644346</v>
+        <v>-4.603927173949685</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.4390997502203689</v>
       </c>
       <c r="E70">
-        <v>-5.767448458980539</v>
+        <v>-0.3333113490941633</v>
       </c>
       <c r="F70">
-        <v>-1.155655510893098</v>
+        <v>-1.013828242757586</v>
       </c>
       <c r="G70">
-        <v>-5.553765726258598</v>
+        <v>-3.920210135360624</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.5616941452204377</v>
       </c>
       <c r="E71">
-        <v>-6.713270068696577</v>
+        <v>-0.004870186265847599</v>
       </c>
       <c r="F71">
-        <v>-1.906474470912125</v>
+        <v>-1.275514475506367</v>
       </c>
       <c r="G71">
-        <v>-4.610981946493871</v>
+        <v>-4.458047984761699</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.6482225486054016</v>
       </c>
       <c r="E72">
-        <v>-6.424520980545492</v>
+        <v>-0.8079678806821394</v>
       </c>
       <c r="F72">
-        <v>-1.423860166734508</v>
+        <v>-1.143780035806564</v>
       </c>
       <c r="G72">
-        <v>-5.233967027165003</v>
+        <v>-3.734273345147458</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.6980347185327407</v>
       </c>
       <c r="E73">
-        <v>-7.296270340918067</v>
+        <v>-0.7497905751055984</v>
       </c>
       <c r="F73">
-        <v>-2.012548573575407</v>
+        <v>-1.519229277451412</v>
       </c>
       <c r="G73">
-        <v>-3.735233403353847</v>
+        <v>-3.6033512007059</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.7131524115117929</v>
       </c>
       <c r="E74">
-        <v>-6.410269872843354</v>
+        <v>-1.568321308940031</v>
       </c>
       <c r="F74">
-        <v>-2.36212872959823</v>
+        <v>-1.545905192923765</v>
       </c>
       <c r="G74">
-        <v>-4.662831710729937</v>
+        <v>-3.841541641710923</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.6949772133402418</v>
       </c>
       <c r="E75">
-        <v>-6.407865253145281</v>
+        <v>-1.542635804368525</v>
       </c>
       <c r="F75">
-        <v>-1.974948977162338</v>
+        <v>-1.507220435213028</v>
       </c>
       <c r="G75">
-        <v>-3.966435282725468</v>
+        <v>-3.51836618616727</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.6432126709923385</v>
       </c>
       <c r="E76">
-        <v>-8.336605731648193</v>
+        <v>-2.434129311414542</v>
       </c>
       <c r="F76">
-        <v>-2.05478288560714</v>
+        <v>-1.698739807107676</v>
       </c>
       <c r="G76">
-        <v>-3.945638435647766</v>
+        <v>-3.539265660156689</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.5588212743881709</v>
       </c>
       <c r="E77">
-        <v>-8.41405622260138</v>
+        <v>-2.392775286776496</v>
       </c>
       <c r="F77">
-        <v>-1.898365582406121</v>
+        <v>-1.425087807225457</v>
       </c>
       <c r="G77">
-        <v>-3.29597035793011</v>
+        <v>-3.378174514215753</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.4404812525743959</v>
       </c>
       <c r="E78">
-        <v>-7.312328309749265</v>
+        <v>-3.238920655109702</v>
       </c>
       <c r="F78">
-        <v>-2.697262986483631</v>
+        <v>-1.79602907346427</v>
       </c>
       <c r="G78">
-        <v>-3.687349672673828</v>
+        <v>-2.933313336285108</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.2869720821354435</v>
       </c>
       <c r="E79">
-        <v>-10.61282507770767</v>
+        <v>-4.860481156250311</v>
       </c>
       <c r="F79">
-        <v>-2.345004718647558</v>
+        <v>-1.706356645376418</v>
       </c>
       <c r="G79">
-        <v>-3.13426345051887</v>
+        <v>-2.105170437999803</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.1002077515605802</v>
       </c>
       <c r="E80">
-        <v>-9.867877518023871</v>
+        <v>-5.21026048860277</v>
       </c>
       <c r="F80">
-        <v>-2.601471408391299</v>
+        <v>-1.77028010111565</v>
       </c>
       <c r="G80">
-        <v>-3.018126202455697</v>
+        <v>-1.925563410857724</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.1195796375012171</v>
       </c>
       <c r="E81">
-        <v>-9.524428992334135</v>
+        <v>-5.598527321546419</v>
       </c>
       <c r="F81">
-        <v>-2.559309992691013</v>
+        <v>-1.936863957451228</v>
       </c>
       <c r="G81">
-        <v>-3.017503819894314</v>
+        <v>-1.715807245489501</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.3691546217020179</v>
       </c>
       <c r="E82">
-        <v>-12.60770391909261</v>
+        <v>-6.425091568270458</v>
       </c>
       <c r="F82">
-        <v>-2.554452446240997</v>
+        <v>-2.030358472735597</v>
       </c>
       <c r="G82">
-        <v>-2.11967724855289</v>
+        <v>-1.233619666603574</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.6419343570225687</v>
       </c>
       <c r="E83">
-        <v>-12.39572152231955</v>
+        <v>-7.927322250834946</v>
       </c>
       <c r="F83">
-        <v>-2.656750021914916</v>
+        <v>-2.233893313807852</v>
       </c>
       <c r="G83">
-        <v>-1.999650109481073</v>
+        <v>-0.423923128063088</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.9312371623725566</v>
       </c>
       <c r="E84">
-        <v>-13.11088077998089</v>
+        <v>-9.531814933440646</v>
       </c>
       <c r="F84">
-        <v>-3.045303207504649</v>
+        <v>-2.04783205473025</v>
       </c>
       <c r="G84">
-        <v>-1.276494541882675</v>
+        <v>-0.5367299673137537</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.22676770167921</v>
       </c>
       <c r="E85">
-        <v>-14.40422654199357</v>
+        <v>-10.1290255570982</v>
       </c>
       <c r="F85">
-        <v>-2.997634805310552</v>
+        <v>-2.535762820899034</v>
       </c>
       <c r="G85">
-        <v>-1.616808691683135</v>
+        <v>-0.0953448621993441</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>1.515733229006762</v>
       </c>
       <c r="E86">
-        <v>-15.74883915824708</v>
+        <v>-12.12672110931591</v>
       </c>
       <c r="F86">
-        <v>-3.229366444406699</v>
+        <v>-2.391426427900443</v>
       </c>
       <c r="G86">
-        <v>-1.534316517935576</v>
+        <v>0.7693265955662795</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>1.784632474104905</v>
       </c>
       <c r="E87">
-        <v>-17.8032764897809</v>
+        <v>-13.13540699520643</v>
       </c>
       <c r="F87">
-        <v>-3.44311422718807</v>
+        <v>-2.332454124127743</v>
       </c>
       <c r="G87">
-        <v>-1.072422583205382</v>
+        <v>0.2982756918744608</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.018720900942913</v>
       </c>
       <c r="E88">
-        <v>-17.61669883219087</v>
+        <v>-16.059927208678</v>
       </c>
       <c r="F88">
-        <v>-3.257362777519114</v>
+        <v>-2.426651923337089</v>
       </c>
       <c r="G88">
-        <v>-0.5045084275800272</v>
+        <v>1.325544593801389</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>2.204474633128017</v>
       </c>
       <c r="E89">
-        <v>-20.09739236511869</v>
+        <v>-16.56806274860469</v>
       </c>
       <c r="F89">
-        <v>-3.145742755094089</v>
+        <v>-2.411566524564707</v>
       </c>
       <c r="G89">
-        <v>-1.030835510141057</v>
+        <v>1.09382957987118</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>2.330849285526835</v>
       </c>
       <c r="E90">
-        <v>-21.11238188682788</v>
+        <v>-19.24135680955273</v>
       </c>
       <c r="F90">
-        <v>-3.374829417073098</v>
+        <v>-3.005669969117707</v>
       </c>
       <c r="G90">
-        <v>-1.211346316215358</v>
+        <v>1.405097003110075</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>2.389696180788397</v>
       </c>
       <c r="E91">
-        <v>-23.88096862631933</v>
+        <v>-21.17500162540595</v>
       </c>
       <c r="F91">
-        <v>-3.664692567028104</v>
+        <v>-2.974055327189864</v>
       </c>
       <c r="G91">
-        <v>-0.6833407870659175</v>
+        <v>0.6066728721308075</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>2.377353328963152</v>
       </c>
       <c r="E92">
-        <v>-25.14518724351467</v>
+        <v>-22.8334873036051</v>
       </c>
       <c r="F92">
-        <v>-3.732385922817476</v>
+        <v>-3.184040665227719</v>
       </c>
       <c r="G92">
-        <v>-0.05608841319466636</v>
+        <v>1.175590123054561</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>2.294303668848078</v>
       </c>
       <c r="E93">
-        <v>-28.32668929997352</v>
+        <v>-25.58897769626637</v>
       </c>
       <c r="F93">
-        <v>-4.045037460023496</v>
+        <v>-2.680365948201327</v>
       </c>
       <c r="G93">
-        <v>-0.3027041925971342</v>
+        <v>1.36346689295374</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>2.144615400228864</v>
       </c>
       <c r="E94">
-        <v>-30.2308492215628</v>
+        <v>-27.32840984735263</v>
       </c>
       <c r="F94">
-        <v>-4.193455219215681</v>
+        <v>-3.175293933821559</v>
       </c>
       <c r="G94">
-        <v>-1.369524182081735</v>
+        <v>0.2880957643412019</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>1.937643131214202</v>
       </c>
       <c r="E95">
-        <v>-31.34148011431399</v>
+        <v>-29.86690482251435</v>
       </c>
       <c r="F95">
-        <v>-4.186645210797266</v>
+        <v>-3.406572455948375</v>
       </c>
       <c r="G95">
-        <v>-1.396541544227727</v>
+        <v>0.2961900481847199</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>1.683933991545099</v>
       </c>
       <c r="E96">
-        <v>-32.91576561105153</v>
+        <v>-32.2467809386094</v>
       </c>
       <c r="F96">
-        <v>-4.303059823749695</v>
+        <v>-3.375989131437017</v>
       </c>
       <c r="G96">
-        <v>-1.765376043849008</v>
+        <v>0.363076310260155</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>1.398707000235168</v>
       </c>
       <c r="E97">
-        <v>-36.6534842802135</v>
+        <v>-35.33317371972215</v>
       </c>
       <c r="F97">
-        <v>-4.480012354866115</v>
+        <v>-3.30242099402699</v>
       </c>
       <c r="G97">
-        <v>-2.02387668173746</v>
+        <v>-0.5349356516314687</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>1.094675271641992</v>
       </c>
       <c r="E98">
-        <v>-38.82495322976455</v>
+        <v>-37.54113537706401</v>
       </c>
       <c r="F98">
-        <v>-4.217240960819667</v>
+        <v>-3.710861624223134</v>
       </c>
       <c r="G98">
-        <v>-3.397117455791463</v>
+        <v>-0.677537400735575</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>0.793961644857984</v>
       </c>
       <c r="E99">
-        <v>-40.74247894238746</v>
+        <v>-39.47100570983184</v>
       </c>
       <c r="F99">
-        <v>-4.522525826712591</v>
+        <v>-3.822705305846915</v>
       </c>
       <c r="G99">
-        <v>-3.101207653309247</v>
+        <v>-1.304293192775935</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>0.500921523994792</v>
       </c>
       <c r="E100">
-        <v>-44.32057116701606</v>
+        <v>-43.12478911326163</v>
       </c>
       <c r="F100">
-        <v>-4.775925071963765</v>
+        <v>-3.993094682030954</v>
       </c>
       <c r="G100">
-        <v>-3.171119754007576</v>
+        <v>-2.262292239839153</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>0.2465283252890974</v>
       </c>
       <c r="E101">
-        <v>-44.30906657879957</v>
+        <v>-44.83986939537165</v>
       </c>
       <c r="F101">
-        <v>-4.300165508044314</v>
+        <v>-4.034813749538145</v>
       </c>
       <c r="G101">
-        <v>-4.096423853324951</v>
+        <v>-2.857839519080804</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>0.01466656286034379</v>
       </c>
       <c r="E102">
-        <v>-47.93081102862511</v>
+        <v>-47.67632890329006</v>
       </c>
       <c r="F102">
-        <v>-5.229787571957614</v>
+        <v>-3.65308051277566</v>
       </c>
       <c r="G102">
-        <v>-4.793412868980949</v>
+        <v>-3.151074400767289</v>
       </c>
     </row>
   </sheetData>
